--- a/output/pdf_financials_xlsx/PEY.xlsx
+++ b/output/pdf_financials_xlsx/PEY.xlsx
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.894</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.057224</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -3000,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002102</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005652</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006185</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005718</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.011905</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.037177</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.013635</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.051057</v>
       </c>
     </row>
     <row r="35">
@@ -3092,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.894</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.057224</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -3110,31 +3110,31 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002102</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005652</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006185</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005718</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.011905</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.037177</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.013635</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.051057</v>
       </c>
     </row>
     <row r="37">
@@ -3752,10 +3752,10 @@
         <v>1122.305</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>15.197</v>
+        <v>7.303</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.109485</v>
+        <v>0.052261</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.017863</v>
@@ -3770,31 +3770,31 @@
         <v>0.08193</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.020417</v>
+        <v>0.018315</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.153247</v>
+        <v>0.147595</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.075101</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.018922</v>
+        <v>0.012737</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.025422</v>
+        <v>0.019704</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.030514</v>
+        <v>0.018609</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.329201</v>
+        <v>0.292024</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.246956</v>
+        <v>0.233321</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.196427</v>
+        <v>0.14537</v>
       </c>
     </row>
     <row r="49">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -41078,7 +41078,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -41440,7 +41440,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -41818,7 +41818,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -42650,7 +42650,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">

--- a/output/pdf_financials_xlsx/PEY.xlsx
+++ b/output/pdf_financials_xlsx/PEY.xlsx
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-31.444</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-15.787</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1906,15 +1906,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>89.886</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>90.264</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -2160,10 +2156,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>121.33</v>
+        <v>89.886</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>106.051</v>
+        <v>90.264</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>87.92028999999999</v>
+        <v>65.134783</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>105.00099</v>
+        <v>89.37029699999999</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2802,10 +2798,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>25.91609659606033</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>14.88623398176349</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -5085,22 +5081,22 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.0009810000000000001</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.001123</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.001266</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.00131</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.000936</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.0009909999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5140,22 +5136,22 @@
         <v>0.1</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.0009810000000000001</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.001123</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.1</v>
+        <v>0.101266</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.05787</v>
+        <v>0.05918</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.057855</v>
+        <v>0.058791</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.1</v>
+        <v>0.100991</v>
       </c>
     </row>
     <row r="72">
@@ -5360,22 +5356,22 @@
         <v>0.029173</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.009815000000000001</v>
+        <v>0.008834</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.070622</v>
+        <v>0.06949900000000001</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.156298</v>
+        <v>0.155032</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.050273</v>
+        <v>0.048963</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.051701</v>
+        <v>0.050765</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.0731</v>
+        <v>0.07210900000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5637,22 +5633,22 @@
         <v>0.6843356172290715</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.6534738846746955</v>
+        <v>0.6540462577826114</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.6034588783956566</v>
+        <v>0.604094776574938</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.416738695792626</v>
+        <v>0.4173527622806022</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.5152045549390908</v>
+        <v>0.5156870696732859</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.5018278555769715</v>
+        <v>0.5021749942236278</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.4117750814066108</v>
+        <v>0.4121225892737542</v>
       </c>
     </row>
     <row r="81">
@@ -6700,10 +6696,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>121.33</v>
+        <v>89.886</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>106.051</v>
+        <v>90.264</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -9900,7 +9896,11 @@
           <t>Current portion of lease obligation</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -16040,7 +16040,11 @@
           <t>Current portion of lease obligation (Note 7)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -30994,7 +30998,11 @@
           <t>Common shares issued under stock option plan and private placement (Note 6)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -37260,7 +37268,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E313" s="5" t="n">
         <v>-31.444</v>
       </c>
@@ -44070,7 +44082,11 @@
           <t>Future income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E386" s="5" t="n">
         <v>31.444</v>
       </c>
